--- a/ILLIA/Octubre/ILLIA-Octubre.xlsx
+++ b/ILLIA/Octubre/ILLIA-Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B74EA42-ADCE-4EFE-AFB1-3E21EF4CB0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DABAA2A-7D9C-4AF4-92FA-9EE070ACD218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="192">
   <si>
     <t>TELEFONO: 11 5320-2676</t>
   </si>
@@ -598,6 +598,12 @@
   </si>
   <si>
     <t>Aumentados 0ct</t>
+  </si>
+  <si>
+    <t>COPELLO MONICA</t>
+  </si>
+  <si>
+    <t>LA PUSIMOS IMPAGA Y HABIA ABONADO $93mil</t>
   </si>
 </sst>
 </file>
@@ -855,7 +861,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -986,6 +992,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFB8CCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1569,7 +1587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="27"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1936,6 +1954,17 @@
     <xf numFmtId="164" fontId="29" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="29" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="29" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1943,7 +1972,6 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1951,12 +1979,8 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1965,40 +1989,17 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -2008,6 +2009,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2027,6 +2029,42 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="23" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="23" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="24" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="24" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="23" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="23" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="23" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2332,16 +2370,16 @@
       <c r="C1" s="89"/>
       <c r="D1" s="89"/>
       <c r="E1" s="89"/>
-      <c r="F1" s="254"/>
-      <c r="G1" s="247"/>
-      <c r="H1" s="247"/>
-      <c r="I1" s="247"/>
-      <c r="J1" s="247"/>
-      <c r="K1" s="247"/>
-      <c r="L1" s="247"/>
-      <c r="M1" s="247"/>
-      <c r="N1" s="247"/>
-      <c r="O1" s="247"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="252"/>
+      <c r="H1" s="252"/>
+      <c r="I1" s="252"/>
+      <c r="J1" s="252"/>
+      <c r="K1" s="252"/>
+      <c r="L1" s="252"/>
+      <c r="M1" s="252"/>
+      <c r="N1" s="252"/>
+      <c r="O1" s="252"/>
       <c r="P1" s="89"/>
       <c r="Q1" s="89"/>
     </row>
@@ -2394,80 +2432,80 @@
       <c r="Q3" s="93"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="261" t="s">
+      <c r="A4" s="246" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="250" t="s">
+      <c r="B4" s="254" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="255" t="s">
+      <c r="C4" s="248" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="255" t="s">
+      <c r="D4" s="248" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="259" t="s">
+      <c r="E4" s="249" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="255" t="s">
+      <c r="F4" s="248" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="255" t="s">
+      <c r="G4" s="248" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="255" t="s">
+      <c r="H4" s="248" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="259" t="s">
+      <c r="I4" s="249" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="260" t="s">
+      <c r="J4" s="261" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="248" t="s">
+      <c r="K4" s="253" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="252" t="s">
+      <c r="L4" s="256" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="248" t="s">
+      <c r="M4" s="253" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="256" t="s">
+      <c r="N4" s="258" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="258" t="s">
+      <c r="P4" s="260" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="252" t="s">
+      <c r="Q4" s="256" t="s">
         <v>74</v>
       </c>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="253"/>
-      <c r="B5" s="251"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="253"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="253"/>
-      <c r="H5" s="253"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="249"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="253"/>
-      <c r="M5" s="249"/>
-      <c r="N5" s="257"/>
+      <c r="A5" s="247"/>
+      <c r="B5" s="255"/>
+      <c r="C5" s="247"/>
+      <c r="D5" s="247"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="247"/>
+      <c r="G5" s="247"/>
+      <c r="H5" s="247"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="250"/>
+      <c r="K5" s="250"/>
+      <c r="L5" s="247"/>
+      <c r="M5" s="250"/>
+      <c r="N5" s="259"/>
       <c r="O5" s="95" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/11</v>
       </c>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="253"/>
+      <c r="P5" s="255"/>
+      <c r="Q5" s="247"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -3615,7 +3653,7 @@
         <v>12</v>
       </c>
       <c r="D24" s="120" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E24" s="105" t="s">
         <v>84</v>
@@ -3866,61 +3904,64 @@
       <c r="A28" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="119" t="s">
+      <c r="B28" s="287" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="120">
+      <c r="C28" s="288">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="D28" s="120" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="105" t="s">
+      <c r="D28" s="288" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="289" t="s">
         <v>143</v>
       </c>
-      <c r="F28" s="97">
+      <c r="F28" s="290">
         <v>3.1</v>
       </c>
-      <c r="G28" s="98">
+      <c r="G28" s="291">
         <v>93000.23</v>
       </c>
-      <c r="H28" s="139"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="101">
+      <c r="H28" s="292"/>
+      <c r="I28" s="293"/>
+      <c r="J28" s="294">
         <f t="shared" si="1"/>
         <v>93000.23</v>
       </c>
-      <c r="K28" s="101">
+      <c r="K28" s="294">
         <f t="shared" si="2"/>
         <v>2790.0068999999999</v>
       </c>
-      <c r="L28" s="98">
+      <c r="L28" s="291">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M28" s="101">
+      <c r="M28" s="294">
         <f t="shared" si="6"/>
         <v>93000</v>
       </c>
-      <c r="N28" s="102">
+      <c r="N28" s="295">
         <v>0</v>
       </c>
-      <c r="O28" s="126">
+      <c r="O28" s="296">
         <f t="shared" si="7"/>
         <v>188790.23</v>
       </c>
-      <c r="P28" s="107">
+      <c r="P28" s="297">
         <f t="shared" si="3"/>
         <v>200118.23</v>
       </c>
-      <c r="Q28" s="127">
+      <c r="Q28" s="298">
         <f t="shared" si="4"/>
         <v>194454.23</v>
       </c>
       <c r="R28" s="60">
         <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
+      </c>
+      <c r="S28" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4447,95 +4488,95 @@
       <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="246" t="s">
+      <c r="D40" s="251" t="s">
         <v>161</v>
       </c>
-      <c r="E40" s="247"/>
-      <c r="F40" s="247"/>
-      <c r="G40" s="247"/>
-      <c r="H40" s="247"/>
-      <c r="I40" s="247"/>
-      <c r="J40" s="247"/>
-      <c r="K40" s="247"/>
-      <c r="L40" s="247"/>
-      <c r="M40" s="247"/>
-      <c r="N40" s="247"/>
-      <c r="O40" s="247"/>
+      <c r="E40" s="252"/>
+      <c r="F40" s="252"/>
+      <c r="G40" s="252"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="252"/>
+      <c r="J40" s="252"/>
+      <c r="K40" s="252"/>
+      <c r="L40" s="252"/>
+      <c r="M40" s="252"/>
+      <c r="N40" s="252"/>
+      <c r="O40" s="252"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="247"/>
-      <c r="E41" s="247"/>
-      <c r="F41" s="247"/>
-      <c r="G41" s="247"/>
-      <c r="H41" s="247"/>
-      <c r="I41" s="247"/>
-      <c r="J41" s="247"/>
-      <c r="K41" s="247"/>
-      <c r="L41" s="247"/>
-      <c r="M41" s="247"/>
-      <c r="N41" s="247"/>
-      <c r="O41" s="247"/>
+      <c r="D41" s="252"/>
+      <c r="E41" s="252"/>
+      <c r="F41" s="252"/>
+      <c r="G41" s="252"/>
+      <c r="H41" s="252"/>
+      <c r="I41" s="252"/>
+      <c r="J41" s="252"/>
+      <c r="K41" s="252"/>
+      <c r="L41" s="252"/>
+      <c r="M41" s="252"/>
+      <c r="N41" s="252"/>
+      <c r="O41" s="252"/>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="247"/>
-      <c r="E42" s="247"/>
-      <c r="F42" s="247"/>
-      <c r="G42" s="247"/>
-      <c r="H42" s="247"/>
-      <c r="I42" s="247"/>
-      <c r="J42" s="247"/>
-      <c r="K42" s="247"/>
-      <c r="L42" s="247"/>
-      <c r="M42" s="247"/>
-      <c r="N42" s="247"/>
-      <c r="O42" s="247"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="252"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="252"/>
+      <c r="H42" s="252"/>
+      <c r="I42" s="252"/>
+      <c r="J42" s="252"/>
+      <c r="K42" s="252"/>
+      <c r="L42" s="252"/>
+      <c r="M42" s="252"/>
+      <c r="N42" s="252"/>
+      <c r="O42" s="252"/>
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="247"/>
-      <c r="E43" s="247"/>
-      <c r="F43" s="247"/>
-      <c r="G43" s="247"/>
-      <c r="H43" s="247"/>
-      <c r="I43" s="247"/>
-      <c r="J43" s="247"/>
-      <c r="K43" s="247"/>
-      <c r="L43" s="247"/>
-      <c r="M43" s="247"/>
-      <c r="N43" s="247"/>
-      <c r="O43" s="247"/>
+      <c r="D43" s="252"/>
+      <c r="E43" s="252"/>
+      <c r="F43" s="252"/>
+      <c r="G43" s="252"/>
+      <c r="H43" s="252"/>
+      <c r="I43" s="252"/>
+      <c r="J43" s="252"/>
+      <c r="K43" s="252"/>
+      <c r="L43" s="252"/>
+      <c r="M43" s="252"/>
+      <c r="N43" s="252"/>
+      <c r="O43" s="252"/>
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="247"/>
-      <c r="E44" s="247"/>
-      <c r="F44" s="247"/>
-      <c r="G44" s="247"/>
-      <c r="H44" s="247"/>
-      <c r="I44" s="247"/>
-      <c r="J44" s="247"/>
-      <c r="K44" s="247"/>
-      <c r="L44" s="247"/>
-      <c r="M44" s="247"/>
-      <c r="N44" s="247"/>
-      <c r="O44" s="247"/>
+      <c r="D44" s="252"/>
+      <c r="E44" s="252"/>
+      <c r="F44" s="252"/>
+      <c r="G44" s="252"/>
+      <c r="H44" s="252"/>
+      <c r="I44" s="252"/>
+      <c r="J44" s="252"/>
+      <c r="K44" s="252"/>
+      <c r="L44" s="252"/>
+      <c r="M44" s="252"/>
+      <c r="N44" s="252"/>
+      <c r="O44" s="252"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="247"/>
-      <c r="E45" s="247"/>
-      <c r="F45" s="247"/>
-      <c r="G45" s="247"/>
-      <c r="H45" s="247"/>
-      <c r="I45" s="247"/>
-      <c r="J45" s="247"/>
-      <c r="K45" s="247"/>
-      <c r="L45" s="247"/>
-      <c r="M45" s="247"/>
-      <c r="N45" s="247"/>
-      <c r="O45" s="247"/>
+      <c r="D45" s="252"/>
+      <c r="E45" s="252"/>
+      <c r="F45" s="252"/>
+      <c r="G45" s="252"/>
+      <c r="H45" s="252"/>
+      <c r="I45" s="252"/>
+      <c r="J45" s="252"/>
+      <c r="K45" s="252"/>
+      <c r="L45" s="252"/>
+      <c r="M45" s="252"/>
+      <c r="N45" s="252"/>
+      <c r="O45" s="252"/>
       <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10006,11 +10047,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -10024,6 +10060,11 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -10073,11 +10114,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="203"/>
-      <c r="B3" s="270" t="s">
+      <c r="B3" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
+      <c r="C3" s="263"/>
+      <c r="D3" s="263"/>
       <c r="E3" s="205"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -10085,9 +10126,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="203"/>
-      <c r="B4" s="272"/>
-      <c r="C4" s="272"/>
-      <c r="D4" s="272"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
       <c r="E4" s="205"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -10125,13 +10166,13 @@
       <c r="I6" s="137"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="279" t="s">
+      <c r="A7" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="280"/>
-      <c r="C7" s="280"/>
-      <c r="D7" s="280"/>
-      <c r="E7" s="281"/>
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="275"/>
       <c r="F7" s="5"/>
       <c r="G7" s="138"/>
       <c r="H7" s="138"/>
@@ -10144,10 +10185,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="276" t="s">
+      <c r="B9" s="269" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="247"/>
+      <c r="C9" s="252"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -10156,8 +10197,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="247"/>
-      <c r="C10" s="247"/>
+      <c r="B10" s="252"/>
+      <c r="C10" s="252"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -10166,8 +10207,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="247"/>
-      <c r="C11" s="247"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="252"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -10186,43 +10227,43 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="282" t="s">
+      <c r="A14" s="276" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="247"/>
-      <c r="C14" s="247"/>
-      <c r="D14" s="247"/>
-      <c r="E14" s="247"/>
+      <c r="B14" s="252"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="252"/>
+      <c r="E14" s="252"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="247"/>
-      <c r="B15" s="247"/>
-      <c r="C15" s="247"/>
-      <c r="D15" s="247"/>
-      <c r="E15" s="247"/>
+      <c r="A15" s="252"/>
+      <c r="B15" s="252"/>
+      <c r="C15" s="252"/>
+      <c r="D15" s="252"/>
+      <c r="E15" s="252"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="247"/>
-      <c r="B16" s="247"/>
-      <c r="C16" s="247"/>
-      <c r="D16" s="247"/>
-      <c r="E16" s="247"/>
+      <c r="A16" s="252"/>
+      <c r="B16" s="252"/>
+      <c r="C16" s="252"/>
+      <c r="D16" s="252"/>
+      <c r="E16" s="252"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="247"/>
-      <c r="B17" s="247"/>
-      <c r="C17" s="247"/>
-      <c r="D17" s="247"/>
-      <c r="E17" s="247"/>
+      <c r="A17" s="252"/>
+      <c r="B17" s="252"/>
+      <c r="C17" s="252"/>
+      <c r="D17" s="252"/>
+      <c r="E17" s="252"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -10744,10 +10785,10 @@
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="277" t="s">
+      <c r="A44" s="270" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="266"/>
+      <c r="B44" s="271"/>
       <c r="C44" s="25"/>
       <c r="D44" s="166">
         <v>60679.199999999997</v>
@@ -10944,10 +10985,10 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="267" t="s">
+      <c r="A54" s="265" t="s">
         <v>173</v>
       </c>
-      <c r="B54" s="278"/>
+      <c r="B54" s="272"/>
       <c r="C54" s="13"/>
       <c r="D54" s="238">
         <v>108000</v>
@@ -11028,10 +11069,10 @@
       <c r="H56" s="38"/>
     </row>
     <row r="57" spans="1:26" s="137" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="285" t="s">
+      <c r="A57" s="279" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="286"/>
+      <c r="B57" s="280"/>
       <c r="C57" s="37"/>
       <c r="D57" s="226">
         <v>450000</v>
@@ -11060,10 +11101,10 @@
       <c r="H58" s="184"/>
     </row>
     <row r="59" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="267" t="s">
+      <c r="A59" s="265" t="s">
         <v>174</v>
       </c>
-      <c r="B59" s="266"/>
+      <c r="B59" s="271"/>
       <c r="C59" s="21"/>
       <c r="D59" s="239">
         <v>17336.11</v>
@@ -11094,10 +11135,10 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="267" t="s">
+      <c r="A60" s="265" t="s">
         <v>164</v>
       </c>
-      <c r="B60" s="266"/>
+      <c r="B60" s="271"/>
       <c r="C60" s="21"/>
       <c r="D60" s="239">
         <v>105205.65</v>
@@ -11120,8 +11161,8 @@
       <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="265"/>
-      <c r="B62" s="266"/>
+      <c r="A62" s="284"/>
+      <c r="B62" s="271"/>
       <c r="C62" s="13"/>
       <c r="D62" s="166"/>
       <c r="E62" s="36"/>
@@ -11176,11 +11217,11 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="267"/>
-      <c r="B64" s="273"/>
+      <c r="A64" s="265"/>
+      <c r="B64" s="266"/>
       <c r="C64" s="41"/>
-      <c r="D64" s="263"/>
-      <c r="E64" s="283"/>
+      <c r="D64" s="282"/>
+      <c r="E64" s="277"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -11204,11 +11245,11 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="274"/>
-      <c r="B65" s="275"/>
+      <c r="A65" s="267"/>
+      <c r="B65" s="268"/>
       <c r="C65" s="41"/>
-      <c r="D65" s="264"/>
-      <c r="E65" s="284"/>
+      <c r="D65" s="283"/>
+      <c r="E65" s="278"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -11232,8 +11273,8 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="267"/>
-      <c r="B66" s="266"/>
+      <c r="A66" s="265"/>
+      <c r="B66" s="271"/>
       <c r="C66" s="13"/>
       <c r="D66" s="170"/>
       <c r="E66" s="42"/>
@@ -11260,8 +11301,8 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="267"/>
-      <c r="B67" s="266"/>
+      <c r="A67" s="265"/>
+      <c r="B67" s="271"/>
       <c r="C67" s="13"/>
       <c r="D67" s="170"/>
       <c r="E67" s="42"/>
@@ -11288,8 +11329,8 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="267"/>
-      <c r="B68" s="266"/>
+      <c r="A68" s="265"/>
+      <c r="B68" s="271"/>
       <c r="C68" s="13"/>
       <c r="D68" s="170"/>
       <c r="E68" s="36"/>
@@ -11323,8 +11364,8 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="267"/>
-      <c r="B70" s="266"/>
+      <c r="A70" s="265"/>
+      <c r="B70" s="271"/>
       <c r="C70" s="13"/>
       <c r="D70" s="170"/>
       <c r="E70" s="36"/>
@@ -11379,8 +11420,8 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="267"/>
-      <c r="B72" s="266"/>
+      <c r="A72" s="265"/>
+      <c r="B72" s="271"/>
       <c r="C72" s="13"/>
       <c r="D72" s="170"/>
       <c r="E72" s="45"/>
@@ -11407,8 +11448,8 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="267"/>
-      <c r="B73" s="266"/>
+      <c r="A73" s="265"/>
+      <c r="B73" s="271"/>
       <c r="C73" s="13"/>
       <c r="D73" s="170"/>
       <c r="E73" s="45"/>
@@ -11435,8 +11476,8 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="268"/>
-      <c r="B74" s="266"/>
+      <c r="A74" s="285"/>
+      <c r="B74" s="271"/>
       <c r="C74" s="46"/>
       <c r="D74" s="170"/>
       <c r="E74" s="45"/>
@@ -12129,17 +12170,17 @@
       <c r="E104" s="136"/>
     </row>
     <row r="105" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="269" t="s">
+      <c r="A105" s="286" t="s">
         <v>162</v>
       </c>
-      <c r="B105" s="269"/>
+      <c r="B105" s="286"/>
       <c r="C105" s="136"/>
       <c r="D105" s="136"/>
       <c r="E105" s="136"/>
     </row>
     <row r="106" spans="1:26" s="137" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="269"/>
-      <c r="B106" s="269"/>
+      <c r="A106" s="286"/>
+      <c r="B106" s="286"/>
       <c r="C106" s="136"/>
       <c r="D106" s="136"/>
       <c r="E106" s="136"/>
@@ -12152,17 +12193,17 @@
       <c r="E107" s="1"/>
     </row>
     <row r="108" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="269" t="s">
+      <c r="A108" s="286" t="s">
         <v>163</v>
       </c>
-      <c r="B108" s="269"/>
+      <c r="B108" s="286"/>
       <c r="C108" s="136"/>
       <c r="D108" s="136"/>
       <c r="E108" s="136"/>
     </row>
     <row r="109" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="269"/>
-      <c r="B109" s="269"/>
+      <c r="A109" s="286"/>
+      <c r="B109" s="286"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -12479,16 +12520,16 @@
     <row r="131" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="132" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="262" t="s">
+      <c r="A133" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="B133" s="247"/>
-      <c r="C133" s="247"/>
+      <c r="B133" s="252"/>
+      <c r="C133" s="252"/>
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="247"/>
-      <c r="B134" s="247"/>
-      <c r="C134" s="247"/>
+      <c r="A134" s="252"/>
+      <c r="B134" s="252"/>
+      <c r="C134" s="252"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="13" t="s">
@@ -13452,17 +13493,6 @@
     <sortCondition ref="E44:E45"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A64:B65"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A133:C134"/>
     <mergeCell ref="D64:D65"/>
     <mergeCell ref="A62:B62"/>
@@ -13475,6 +13505,17 @@
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A105:B106"/>
     <mergeCell ref="A108:B109"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A64:B65"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A57:B57"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
